--- a/data/trans_dic/Q20C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,05</t>
+          <t>0,0; 56,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,31</t>
+          <t>0,0; 55,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,42; 83,28</t>
+          <t>15,09; 83,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,83</t>
+          <t>0,0; 75,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 45,73</t>
+          <t>5,98; 43,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,63</t>
+          <t>8,15; 58,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,52</t>
+          <t>0,0; 82,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,63</t>
+          <t>0,0; 57,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,18</t>
+          <t>0,0; 83,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 51,84</t>
+          <t>1,69; 50,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 67,54</t>
+          <t>10,41; 67,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 52,7</t>
+          <t>3,82; 47,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,82</t>
+          <t>0,0; 59,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 45,36</t>
+          <t>6,91; 51,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 40,52</t>
+          <t>8,18; 40,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,85</t>
+          <t>0,0; 46,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 43,33</t>
+          <t>4,15; 38,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,75</t>
+          <t>0,0; 56,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,85</t>
+          <t>13,15; 85,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,68</t>
+          <t>0,0; 53,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 66,9</t>
+          <t>10,23; 67,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 44,93</t>
+          <t>6,08; 43,28</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,35</t>
+          <t>0,0; 78,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,37</t>
+          <t>0,0; 50,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 75,87</t>
+          <t>13,67; 74,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,59</t>
+          <t>0,0; 56,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,61</t>
+          <t>0,0; 71,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 65,83</t>
+          <t>7,54; 61,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 53,97</t>
+          <t>0,0; 54,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,59</t>
+          <t>0,0; 56,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 55,82</t>
+          <t>6,92; 54,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 44,29</t>
+          <t>4,98; 44,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,71; 60,87</t>
+          <t>15,13; 59,93</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,56</t>
+          <t>0,0; 58,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,36</t>
+          <t>0,0; 37,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14,08; 73,45</t>
+          <t>13,9; 72,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,05</t>
+          <t>0,0; 72,24</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,52</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25,26; 78,67</t>
+          <t>24,21; 79,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,28</t>
+          <t>0,0; 54,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,48</t>
+          <t>0,0; 64,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,34</t>
+          <t>0,0; 41,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,17</t>
+          <t>0,0; 62,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,83</t>
+          <t>0,0; 35,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,61; 63,58</t>
+          <t>18,51; 64,77</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>30,25; 84,84</t>
+          <t>29,07; 80,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,73</t>
+          <t>0,0; 63,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 86,9</t>
+          <t>12,82; 88,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,41</t>
+          <t>0,0; 58,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,0</t>
+          <t>0,0; 35,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,86; 71,27</t>
+          <t>21,09; 77,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 60,61</t>
+          <t>7,63; 60,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,06; 45,05</t>
+          <t>10,94; 46,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,09; 50,47</t>
+          <t>15,52; 49,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 57,92</t>
+          <t>17,66; 57,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,69; 62,18</t>
+          <t>15,31; 63,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,47; 39,2</t>
+          <t>11,09; 41,82</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,34</t>
+          <t>0,0; 67,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,08</t>
+          <t>0,0; 83,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,28</t>
+          <t>0,0; 44,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,31</t>
+          <t>0,0; 41,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,2; 69,7</t>
+          <t>9,59; 67,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,98; 71,22</t>
+          <t>14,89; 72,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,83</t>
+          <t>0,0; 71,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 54,47</t>
+          <t>6,99; 52,27</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19,76; 64,16</t>
+          <t>18,68; 63,19</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 43,45</t>
+          <t>5,48; 44,47</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 24,69</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14,05; 43,79</t>
+          <t>13,46; 42,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,37; 30,79</t>
+          <t>10,33; 31,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,87; 38,72</t>
+          <t>11,27; 35,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17,12; 40,07</t>
+          <t>16,52; 38,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 30,04</t>
+          <t>9,32; 30,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,96; 37,77</t>
+          <t>17,77; 37,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,48</t>
+          <t>15,44; 38,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,24; 29,07</t>
+          <t>11,39; 29,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,61; 30,44</t>
+          <t>13,58; 31,82</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,01; 32,48</t>
+          <t>17,14; 31,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16,72; 33,58</t>
+          <t>17,33; 34,35</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,63; 30,9</t>
+          <t>16,36; 30,6</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado</t>
+          <t>Población con mayor tiempo de espera (más de 7 meses) para ser hopitalizado (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1215</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6240</t>
+          <t>0; 6545</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1647</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5235</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>867; 4683</t>
+          <t>848; 4682</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2061</t>
+          <t>0; 2028</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1215</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1385; 9608</t>
+          <t>1256; 9234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5758</t>
+          <t>829; 5963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4098</t>
+          <t>0; 4249</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1557</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5783</t>
+          <t>0; 5882</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5527</t>
+          <t>0; 5520</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>167; 7212</t>
+          <t>235; 7013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>952; 6081</t>
+          <t>937; 6107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>899; 7747</t>
+          <t>562; 6944</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2020</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 3639</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958; 6395</t>
+          <t>975; 7199</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1944; 10094</t>
+          <t>2038; 10156</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6695</t>
+          <t>0; 6644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>862; 8667</t>
+          <t>831; 7608</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 732</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1569</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4406</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1124</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1711</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5982</t>
+          <t>927; 6031</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 2956</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1298</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1798</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>910; 5940</t>
+          <t>909; 6031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>853; 6019</t>
+          <t>815; 5799</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3699</t>
+          <t>0; 3763</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4037</t>
+          <t>0; 4233</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>978; 6573</t>
+          <t>1184; 6451</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>0; 3639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5387</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>904; 7317</t>
+          <t>838; 6871</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>297; 3451</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>0; 3639</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>847; 6870</t>
+          <t>851; 6765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1016; 8619</t>
+          <t>969; 8631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2365; 9166</t>
+          <t>2278; 9024</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1198</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4128</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 771</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1786</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1340</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 4784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>948; 4943</t>
+          <t>935; 4903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2561</t>
+          <t>0; 2465</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2802</t>
+          <t>0; 3615</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1571; 4893</t>
+          <t>1506; 4959</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1573</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4501</t>
+          <t>0; 4390</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 1953</t>
+          <t>0; 2107</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4913</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5792</t>
+          <t>0; 5800</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 4441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1578; 6043</t>
+          <t>1759; 6156</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3803; 10664</t>
+          <t>3655; 10063</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5885</t>
+          <t>0; 6029</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1113; 7712</t>
+          <t>1138; 7858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 4610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5844</t>
+          <t>0; 5745</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3142; 10735</t>
+          <t>3176; 11603</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>774; 6654</t>
+          <t>838; 6607</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1467; 6569</t>
+          <t>1595; 6806</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4634; 14536</t>
+          <t>4471; 14299</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4276; 14246</t>
+          <t>4344; 14195</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3116; 12347</t>
+          <t>3040; 12628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2351; 8805</t>
+          <t>2492; 9392</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3805</t>
+          <t>0; 3823</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5224</t>
+          <t>0; 5293</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 5136</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3205</t>
+          <t>0; 3049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>768; 5822</t>
+          <t>801; 5665</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2289; 10887</t>
+          <t>2276; 11022</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5660</t>
+          <t>0; 5644</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 1005</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>985; 7628</t>
+          <t>979; 7319</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4278; 13890</t>
+          <t>4045; 13681</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1081; 8465</t>
+          <t>1068; 8663</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3888</t>
+          <t>0; 2894</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4680; 14587</t>
+          <t>4484; 14136</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5604; 18409</t>
+          <t>6173; 18557</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6087; 19857</t>
+          <t>5778; 18392</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9714; 22730</t>
+          <t>9372; 21865</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3990; 14723</t>
+          <t>4570; 14833</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14580; 30653</t>
+          <t>14419; 30731</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9952; 23784</t>
+          <t>9300; 23282</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>4944; 12785</t>
+          <t>5009; 12850</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11208; 25061</t>
+          <t>11181; 26193</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23978; 45776</t>
+          <t>24158; 44475</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18642; 37453</t>
+          <t>19332; 38315</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>15738; 31122</t>
+          <t>16474; 30813</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q20C_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q20C_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,69</t>
+          <t>0,0; 53,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,23</t>
+          <t>0,0; 55,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,09; 83,25</t>
+          <t>15,22; 83,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,57</t>
+          <t>0,0; 66,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 43,95</t>
+          <t>6,55; 44,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 58,65</t>
+          <t>8,2; 58,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,44</t>
+          <t>0,0; 78,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -862,27 +862,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,6</t>
+          <t>0,0; 57,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,07</t>
+          <t>0,0; 83,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 50,41</t>
+          <t>5,96; 53,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 67,82</t>
+          <t>10,8; 69,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 47,24</t>
+          <t>5,9; 47,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,27 +892,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,76</t>
+          <t>0,0; 60,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 51,06</t>
+          <t>6,86; 51,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 40,77</t>
+          <t>7,72; 41,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,49</t>
+          <t>0,0; 49,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 38,03</t>
+          <t>5,85; 45,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,4</t>
+          <t>0,0; 58,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,15; 85,54</t>
+          <t>12,97; 84,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,79</t>
+          <t>0,0; 54,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 67,93</t>
+          <t>10,42; 68,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 43,28</t>
+          <t>4,91; 43,89</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -1142,57 +1142,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,7</t>
+          <t>0,0; 77,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,71</t>
+          <t>0,0; 49,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 74,47</t>
+          <t>17,48; 82,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,03</t>
+          <t>0,0; 56,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,68</t>
+          <t>0,0; 71,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 61,81</t>
+          <t>7,26; 61,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,52</t>
+          <t>4,72; 55,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,03</t>
+          <t>0,0; 56,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 54,97</t>
+          <t>6,9; 55,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 44,34</t>
+          <t>4,97; 46,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,13; 59,93</t>
+          <t>19,03; 66,37</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,79</t>
+          <t>0,0; 58,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,29 +1292,29 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 78,67</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,11</t>
+          <t>0,0; 35,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,9; 72,86</t>
+          <t>13,99; 85,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,24</t>
+          <t>0,0; 74,6</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 77,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24,21; 79,72</t>
+          <t>24,2; 78,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,88</t>
+          <t>0,0; 56,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,15</t>
+          <t>0,0; 61,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,21</t>
+          <t>0,0; 50,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,25</t>
+          <t>0,0; 62,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,08</t>
+          <t>0,0; 39,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,51; 64,77</t>
+          <t>16,97; 64,75</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,07; 80,06</t>
+          <t>26,71; 80,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,24</t>
+          <t>0,0; 62,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 88,54</t>
+          <t>12,27; 88,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,51</t>
+          <t>0,0; 48,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,39</t>
+          <t>0,0; 36,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,09; 77,03</t>
+          <t>20,99; 75,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 60,17</t>
+          <t>7,89; 59,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,94; 46,68</t>
+          <t>13,76; 47,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 49,64</t>
+          <t>16,05; 51,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,66; 57,71</t>
+          <t>18,35; 57,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,31; 63,6</t>
+          <t>15,42; 63,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,09; 41,82</t>
+          <t>12,26; 39,26</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,66</t>
+          <t>0,0; 65,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,17</t>
+          <t>0,0; 81,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,26</t>
+          <t>0,0; 44,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,2</t>
+          <t>0,0; 36,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,59; 67,83</t>
+          <t>9,15; 71,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,89; 72,1</t>
+          <t>15,53; 69,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,62</t>
+          <t>0,0; 70,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,22 +1737,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,99; 52,27</t>
+          <t>7,21; 53,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18,68; 63,19</t>
+          <t>18,87; 62,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 44,47</t>
+          <t>5,46; 44,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,69</t>
+          <t>0,0; 21,47</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,46; 42,44</t>
+          <t>13,49; 44,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,33; 31,04</t>
+          <t>10,52; 32,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,27; 35,87</t>
+          <t>11,01; 35,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16,52; 38,54</t>
+          <t>18,9; 40,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 30,26</t>
+          <t>8,32; 30,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,77; 37,86</t>
+          <t>17,42; 37,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,44; 38,64</t>
+          <t>16,25; 39,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,39; 29,22</t>
+          <t>12,33; 28,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,58; 31,82</t>
+          <t>13,24; 31,22</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17,14; 31,56</t>
+          <t>16,95; 31,65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17,33; 34,35</t>
+          <t>17,23; 33,82</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,36; 30,6</t>
+          <t>17,57; 33,27</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>478</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1680</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6545</t>
+          <t>0; 6199</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2472</t>
+          <t>0; 2141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>848; 4682</t>
+          <t>856; 4685</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>0; 2000</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1256; 9234</t>
+          <t>1376; 9362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>829; 5963</t>
+          <t>833; 5938</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4249</t>
+          <t>0; 4024</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>932</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>4647</t>
         </is>
       </c>
     </row>
@@ -2422,27 +2422,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5882</t>
+          <t>0; 5916</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5520</t>
+          <t>0; 5552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>235; 7013</t>
+          <t>921; 8228</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>937; 6107</t>
+          <t>973; 6246</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>562; 6944</t>
+          <t>867; 7019</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,27 +2452,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3639</t>
+          <t>0; 3967</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>975; 7199</t>
+          <t>968; 7232</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2038; 10156</t>
+          <t>1923; 10288</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 7056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>831; 7608</t>
+          <t>1287; 9915</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>978</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2512</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 4521</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>927; 6031</t>
+          <t>914; 5933</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2956</t>
+          <t>0; 3076</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>909; 6031</t>
+          <t>925; 6121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>815; 5799</t>
+          <t>655; 5850</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>7307</t>
         </is>
       </c>
     </row>
@@ -2838,57 +2838,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3763</t>
+          <t>0; 3693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4233</t>
+          <t>0; 4141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1184; 6451</t>
+          <t>1880; 8915</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3639</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5393</t>
+          <t>0; 5413</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>838; 6871</t>
+          <t>807; 6890</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3486</t>
+          <t>336; 3927</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3639</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>851; 6765</t>
+          <t>849; 6878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>969; 8631</t>
+          <t>967; 9043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2278; 9024</t>
+          <t>3400; 11857</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>384</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 4118</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2283</t>
+          <t>0; 1926</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1130</t>
+          <t>0; 1195</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>935; 4903</t>
+          <t>942; 5752</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2465</t>
+          <t>0; 2718</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>349</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3577</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3615</t>
+          <t>0; 2802</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1506; 4959</t>
+          <t>1477; 4800</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3279,32 +3279,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4390</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2107</t>
+          <t>0; 2052</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 4799</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5800</t>
+          <t>0; 5798</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4441</t>
+          <t>0; 5036</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1759; 6156</t>
+          <t>1598; 6097</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>6662</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3655; 10063</t>
+          <t>3358; 10082</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6029</t>
+          <t>0; 5985</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1138; 7858</t>
+          <t>1089; 7825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4610</t>
+          <t>0; 4492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5745</t>
+          <t>0; 5961</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3176; 11603</t>
+          <t>3162; 11377</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>838; 6607</t>
+          <t>867; 6503</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1595; 6806</t>
+          <t>2660; 9208</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4471; 14299</t>
+          <t>4623; 14972</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4344; 14195</t>
+          <t>4513; 14178</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3040; 12628</t>
+          <t>3062; 12611</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2492; 9392</t>
+          <t>3513; 11247</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>666</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>666</t>
         </is>
       </c>
     </row>
@@ -3665,37 +3665,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 3725</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5293</t>
+          <t>0; 5208</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5136</t>
+          <t>0; 5119</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3049</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>801; 5665</t>
+          <t>765; 5993</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2276; 11022</t>
+          <t>2374; 10672</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 5644</t>
+          <t>0; 5586</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,22 +3705,22 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>979; 7319</t>
+          <t>1009; 7535</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4045; 13681</t>
+          <t>4086; 13628</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1068; 8663</t>
+          <t>1063; 8597</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 2894</t>
+          <t>0; 2893</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>28046</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4484; 14136</t>
+          <t>4492; 14910</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6173; 18557</t>
+          <t>6287; 19299</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5778; 18392</t>
+          <t>5647; 18297</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9372; 21865</t>
+          <t>11824; 25634</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4570; 14833</t>
+          <t>4076; 14980</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14419; 30731</t>
+          <t>14137; 30575</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9300; 23282</t>
+          <t>9792; 23513</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5009; 12850</t>
+          <t>6284; 14721</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11181; 26193</t>
+          <t>10902; 25698</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24158; 44475</t>
+          <t>23894; 44613</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19332; 38315</t>
+          <t>19221; 37717</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16474; 30813</t>
+          <t>19951; 37767</t>
         </is>
       </c>
     </row>
